--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J183-Diplome-EPARS.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J183-Diplome-EPARS.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250917120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-17T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -174,31 +174,31 @@
     <t>DIP324</t>
   </si>
   <si>
-    <t>Licence + Master mention clinique, psychopatho et psycho santé + Attest stage</t>
+    <t>Licence + Master mention psychologie clinique, psychopatho et psycho santé + Attest stage</t>
   </si>
   <si>
     <t>DIP325</t>
   </si>
   <si>
-    <t>Licence + Master mention sociale, du travail et des organisations + Attest stage</t>
+    <t>Licence + Master mention psychologie sociale, du travail et des organisations + Attest stage</t>
   </si>
   <si>
     <t>DIP326</t>
   </si>
   <si>
-    <t>Licence + Master mention éducation et de la formation + Attest stage</t>
+    <t>Licence + Master mention psychologie de l'éducation et de la formation + Attest stage</t>
   </si>
   <si>
     <t>DIP327</t>
   </si>
   <si>
-    <t>Licence + Master mention psychopatho clinique psychanalytique + Attest stage</t>
+    <t>Licence + Master mention psychologie: psychopatho clinique psychanalytique + Attest stage</t>
   </si>
   <si>
     <t>DIP328</t>
   </si>
   <si>
-    <t>Master de Psychanalyse</t>
+    <t>Diplôme de niveau Master en psychanalyse</t>
   </si>
   <si>
     <t>DIP329</t>
